--- a/outputs/ioannina_dc_detailed_cashflows.xlsx
+++ b/outputs/ioannina_dc_detailed_cashflows.xlsx
@@ -524,31 +524,31 @@
         <v>0.0675</v>
       </c>
       <c r="F2" t="n">
-        <v>18848395.2069507</v>
+        <v>28709474.06741089</v>
       </c>
       <c r="G2" t="n">
-        <v>8968630.088112429</v>
+        <v>6428777.151472151</v>
       </c>
       <c r="H2" t="n">
-        <v>0.109434746312392</v>
+        <v>0.1020912046335986</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1503987110733805</v>
+        <v>0.1310390586458196</v>
       </c>
       <c r="J2" t="n">
         <v>0.507733496709994</v>
       </c>
       <c r="K2" t="n">
-        <v>12840685.2499564</v>
+        <v>14125961.79936943</v>
       </c>
       <c r="L2" t="n">
-        <v>193898259.0026802</v>
+        <v>200503862.3377415</v>
       </c>
       <c r="M2" t="n">
-        <v>79.0321091383325</v>
+        <v>74.50345527759279</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8179309439305656</v>
+        <v>0.7676772559278472</v>
       </c>
     </row>
     <row r="3">
@@ -572,28 +572,28 @@
         <v>0.07500000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-20181091.52791512</v>
+        <v>-10793139.50970074</v>
       </c>
       <c r="G3" t="n">
-        <v>-21840022.55946857</v>
+        <v>-23138096.11709538</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06793610784517046</v>
+        <v>0.07128056832145824</v>
       </c>
       <c r="I3" t="n">
-        <v>0.074700027566028</v>
+        <v>0.07813787486861934</v>
       </c>
       <c r="J3" t="n">
         <v>0.2948794692125012</v>
       </c>
       <c r="K3" t="n">
-        <v>10658743.65432059</v>
+        <v>11712826.5871211</v>
       </c>
       <c r="L3" t="n">
-        <v>144824036.4980057</v>
+        <v>149593329.9874509</v>
       </c>
       <c r="M3" t="n">
-        <v>104.4943327373835</v>
+        <v>97.07369354165563</v>
       </c>
       <c r="N3" t="n">
         <v>0.99</v>
@@ -620,31 +620,31 @@
         <v>0.0625</v>
       </c>
       <c r="F4" t="n">
-        <v>47512520.51898246</v>
+        <v>57302647.96446042</v>
       </c>
       <c r="G4" t="n">
-        <v>30654459.37205216</v>
+        <v>26536572.47844311</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1361645741717247</v>
+        <v>0.1218594857734602</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1943353346475581</v>
+        <v>0.1633272105064206</v>
       </c>
       <c r="J4" t="n">
         <v>0.6636364609719412</v>
       </c>
       <c r="K4" t="n">
-        <v>14557093.66537984</v>
+        <v>16022039.22699021</v>
       </c>
       <c r="L4" t="n">
-        <v>237424902.3337332</v>
+        <v>245634703.5953456</v>
       </c>
       <c r="M4" t="n">
-        <v>66.28681470650376</v>
+        <v>63.15442022028707</v>
       </c>
       <c r="N4" t="n">
-        <v>0.668086054156075</v>
+        <v>0.6346559945947606</v>
       </c>
     </row>
     <row r="5">
@@ -668,31 +668,31 @@
         <v>0.075</v>
       </c>
       <c r="F5" t="n">
-        <v>14853601.20234673</v>
+        <v>21463614.88270685</v>
       </c>
       <c r="G5" t="n">
-        <v>7879296.166277278</v>
+        <v>7450283.980614157</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1203530443522222</v>
+        <v>0.1125671300393717</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1647692368597514</v>
+        <v>0.1448347612192914</v>
       </c>
       <c r="J5" t="n">
         <v>0.3517239255768159</v>
       </c>
       <c r="K5" t="n">
-        <v>7439876.971696155</v>
+        <v>8185216.381096346</v>
       </c>
       <c r="L5" t="n">
-        <v>101111557.9134374</v>
+        <v>104564541.8104052</v>
       </c>
       <c r="M5" t="n">
-        <v>42.47649532102881</v>
+        <v>39.46717845739984</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7455400636052116</v>
+        <v>0.6890124325705802</v>
       </c>
     </row>
     <row r="6">
@@ -716,31 +716,31 @@
         <v>0.08249999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-5124692.532248553</v>
+        <v>922253.125958994</v>
       </c>
       <c r="G6" t="n">
-        <v>-7863777.187460354</v>
+        <v>-7863282.221261188</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07891642473714933</v>
+        <v>0.08146622280382843</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09174281210426949</v>
+        <v>0.09252394504872818</v>
       </c>
       <c r="J6" t="n">
         <v>0.1482881492962099</v>
       </c>
       <c r="K6" t="n">
-        <v>6180864.755955399</v>
+        <v>6792844.44578083</v>
       </c>
       <c r="L6" t="n">
-        <v>76348482.06112058</v>
+        <v>78871307.12444469</v>
       </c>
       <c r="M6" t="n">
-        <v>56.04542450632091</v>
+        <v>51.34733123845484</v>
       </c>
       <c r="N6" t="n">
-        <v>0.99</v>
+        <v>0.9349247339208265</v>
       </c>
     </row>
     <row r="7">
@@ -764,31 +764,31 @@
         <v>0.06999999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>29460658.55464786</v>
+        <v>36314991.24868894</v>
       </c>
       <c r="G7" t="n">
-        <v>18923262.12484609</v>
+        <v>17880640.33141899</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1468460717256012</v>
+        <v>0.1324209138195765</v>
       </c>
       <c r="I7" t="n">
-        <v>0.207467971917637</v>
+        <v>0.1768707145711256</v>
       </c>
       <c r="J7" t="n">
         <v>0.4998380009649149</v>
       </c>
       <c r="K7" t="n">
-        <v>8431163.324061941</v>
+        <v>9280256.792448025</v>
       </c>
       <c r="L7" t="n">
-        <v>122779786.803905</v>
+        <v>127033975.4113239</v>
       </c>
       <c r="M7" t="n">
-        <v>35.74199703374037</v>
+        <v>33.54374385334992</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6073375702293046</v>
+        <v>0.5663572414128574</v>
       </c>
     </row>
     <row r="8">
@@ -812,31 +812,31 @@
         <v>0.0725</v>
       </c>
       <c r="F8" t="n">
-        <v>15162694.52948594</v>
+        <v>22221159.8259584</v>
       </c>
       <c r="G8" t="n">
-        <v>12848559.26469032</v>
+        <v>7580409.437559079</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1468862587547607</v>
+        <v>0.1117134720696932</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2373176576043231</v>
+        <v>0.1440105292618904</v>
       </c>
       <c r="J8" t="n">
         <v>0.3897511735712555</v>
       </c>
       <c r="K8" t="n">
-        <v>6816309.643850001</v>
+        <v>8404928.388572972</v>
       </c>
       <c r="L8" t="n">
-        <v>95827870.43114829</v>
+        <v>111066709.1152155</v>
       </c>
       <c r="M8" t="n">
-        <v>47.11568896086638</v>
+        <v>43.84489589503059</v>
       </c>
       <c r="N8" t="n">
-        <v>0.72740700754115</v>
+        <v>0.6738840660117571</v>
       </c>
     </row>
     <row r="9">
@@ -860,28 +860,28 @@
         <v>0.07999999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-8214265.74810677</v>
+        <v>-241280.897524979</v>
       </c>
       <c r="G9" t="n">
-        <v>-7595647.098837998</v>
+        <v>-9193496.719747262</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05724352943658795</v>
+        <v>0.07963825972010186</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05497024198223033</v>
+        <v>0.08937749408663331</v>
       </c>
       <c r="J9" t="n">
         <v>0.178260484646233</v>
       </c>
       <c r="K9" t="n">
-        <v>5626503.678769202</v>
+        <v>6919930.547564576</v>
       </c>
       <c r="L9" t="n">
-        <v>71668866.2929792</v>
+        <v>82850197.0830677</v>
       </c>
       <c r="M9" t="n">
-        <v>63.79630851013336</v>
+        <v>57.17361025114556</v>
       </c>
       <c r="N9" t="n">
         <v>0.99</v>
@@ -908,31 +908,31 @@
         <v>0.06749999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>32839443.94317293</v>
+        <v>38456396.6070262</v>
       </c>
       <c r="G10" t="n">
-        <v>28053565.04918686</v>
+        <v>19006342.65649394</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2059342788925377</v>
+        <v>0.1321434714806279</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3402145803324944</v>
+        <v>0.1773693439397163</v>
       </c>
       <c r="J10" t="n">
         <v>0.5438723944666876</v>
       </c>
       <c r="K10" t="n">
-        <v>7746135.831286602</v>
+        <v>9562456.29931725</v>
       </c>
       <c r="L10" t="n">
-        <v>116978453.6600438</v>
+        <v>135737782.9664733</v>
       </c>
       <c r="M10" t="n">
-        <v>38.95861646275693</v>
+        <v>37.21877027247553</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5811357100930475</v>
+        <v>0.5537461772331778</v>
       </c>
     </row>
   </sheetData>
@@ -946,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE13"/>
+  <dimension ref="A1:AE18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1282,16 +1282,16 @@
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9174311926605504</v>
+        <v>0.9259259259259258</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8849557522123894</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="AB3" t="n">
-        <v>-42359633.02752294</v>
+        <v>-42751851.85185184</v>
       </c>
       <c r="AC3" t="n">
-        <v>-16344070.79646018</v>
+        <v>-16490000</v>
       </c>
       <c r="AD3" t="n">
         <v>-115430000</v>
@@ -1381,16 +1381,16 @@
         <v>0.6636364609719412</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.84167999326656</v>
+        <v>0.8573388203017832</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7831466833737961</v>
+        <v>0.7971938775510203</v>
       </c>
       <c r="AB4" t="n">
-        <v>3828485.817692114</v>
+        <v>3899711.934156379</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1805518.015204328</v>
+        <v>-1837903.343123729</v>
       </c>
       <c r="AD4" t="n">
         <v>-110881376</v>
@@ -1480,16 +1480,16 @@
         <v>1.300722246182173</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7721834800610642</v>
+        <v>0.7938322410201696</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.6930501622776957</v>
+        <v>0.7117802478134109</v>
       </c>
       <c r="AB5" t="n">
-        <v>6884222.113944937</v>
+        <v>7077226.604176192</v>
       </c>
       <c r="AC5" t="n">
-        <v>1428499.280534642</v>
+        <v>1467105.308162121</v>
       </c>
       <c r="AD5" t="n">
         <v>-101966108.72</v>
@@ -1579,16 +1579,16 @@
         <v>1.644329088160964</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7084252110651963</v>
+        <v>0.7350298527964533</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6133187276793768</v>
+        <v>0.6355180784048311</v>
       </c>
       <c r="AB6" t="n">
-        <v>7984220.964454188</v>
+        <v>8284065.372790675</v>
       </c>
       <c r="AC6" t="n">
-        <v>2708593.075594517</v>
+        <v>2806631.835775819</v>
       </c>
       <c r="AD6" t="n">
         <v>-90695729.23639999</v>
@@ -1678,16 +1678,16 @@
         <v>1.827786211402674</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6499313862983452</v>
+        <v>0.6805831970337529</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5427599359994485</v>
+        <v>0.5674268557185992</v>
       </c>
       <c r="AB7" t="n">
-        <v>8142217.641310686</v>
+        <v>8526217.736350548</v>
       </c>
       <c r="AC7" t="n">
-        <v>3079468.53113781</v>
+        <v>3219421.755384827</v>
       </c>
       <c r="AD7" t="n">
         <v>-78167918.12746999</v>
@@ -1777,16 +1777,16 @@
         <v>1.929500468804541</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5962673268792158</v>
+        <v>0.6301696268831045</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.4803185274331404</v>
+        <v>0.5066311211773206</v>
       </c>
       <c r="AB8" t="n">
-        <v>7885617.378020254</v>
+        <v>8333974.271001034</v>
       </c>
       <c r="AC8" t="n">
-        <v>3060051.616051818</v>
+        <v>3227685.988683013</v>
       </c>
       <c r="AD8" t="n">
         <v>-64942948.3487425</v>
@@ -1876,16 +1876,16 @@
         <v>1.966906801747874</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.5470342448433172</v>
+        <v>0.5834903952621338</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.4250606437461419</v>
+        <v>0.4523492153368934</v>
       </c>
       <c r="AB9" t="n">
-        <v>7374763.480736149</v>
+        <v>7866241.828373997</v>
       </c>
       <c r="AC9" t="n">
-        <v>2816990.035523957</v>
+        <v>2997838.663562874</v>
       </c>
       <c r="AD9" t="n">
         <v>-51461592.19918655</v>
@@ -1975,16 +1975,16 @@
         <v>2.005031669439255</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.501866279672768</v>
+        <v>0.5402688845019757</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.3761598617222495</v>
+        <v>0.403883227979369</v>
       </c>
       <c r="AB10" t="n">
-        <v>6896981.371950789</v>
+        <v>7424735.598264084</v>
       </c>
       <c r="AC10" t="n">
-        <v>2591206.34803951</v>
+        <v>2782180.90419116</v>
       </c>
       <c r="AD10" t="n">
         <v>-37718924.77700423</v>
@@ -2074,16 +2074,16 @@
         <v>2.043888702775874</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.4604277795163009</v>
+        <v>0.5002489671314589</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.3328848333825217</v>
+        <v>0.3606100249815795</v>
       </c>
       <c r="AB11" t="n">
-        <v>6450131.393011754</v>
+        <v>7007986.291804734</v>
       </c>
       <c r="AC11" t="n">
-        <v>2381760.047993435</v>
+        <v>2580131.217393386</v>
       </c>
       <c r="AD11" t="n">
         <v>-23709927.75300213</v>
@@ -2173,16 +2173,16 @@
         <v>2.083491786777922</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.4224108068956888</v>
+        <v>0.4631934880846841</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.2945883481261255</v>
+        <v>0.3219732365906959</v>
       </c>
       <c r="AB12" t="n">
-        <v>6032212.235685803</v>
+        <v>6614606.87250929</v>
       </c>
       <c r="AC12" t="n">
-        <v>2187716.229356825</v>
+        <v>2391086.000476955</v>
       </c>
       <c r="AD12" t="n">
         <v>-9429487.628809441</v>
@@ -2260,34 +2260,529 @@
         <v>29349350.59223976</v>
       </c>
       <c r="V13" t="n">
-        <v>237424902.3337332</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>251981995.999113</v>
+        <v>14557093.66537984</v>
       </c>
       <c r="X13" t="n">
-        <v>215778555.4532588</v>
+        <v>7703003.711765435</v>
       </c>
       <c r="Y13" t="n">
         <v>2.123855065208674</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.3875328503630173</v>
+        <v>0.4288828593376705</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.2606976532089606</v>
+        <v>0.2874761040988356</v>
       </c>
       <c r="AB13" t="n">
-        <v>97651301.14969869</v>
+        <v>6243287.954854397</v>
       </c>
       <c r="AC13" t="n">
-        <v>56252963.01948415</v>
+        <v>2214429.496917197</v>
       </c>
       <c r="AD13" t="n">
-        <v>242552508.3703036</v>
+        <v>5127606.0365704</v>
       </c>
       <c r="AE13" t="n">
-        <v>213920258.2419197</v>
+        <v>5844706.500426317</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Turnkey</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2038</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>17062021.09778262</v>
+      </c>
+      <c r="L14" t="n">
+        <v>16720780.67582697</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1881724.279968644</v>
+      </c>
+      <c r="N14" t="n">
+        <v>14839056.39585832</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1584864.931980947</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5269225.021633459</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6854089.953614406</v>
+      </c>
+      <c r="U14" t="n">
+        <v>24080125.57060631</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>14839056.39585832</v>
+      </c>
+      <c r="X14" t="n">
+        <v>7984966.442243917</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.16499294527542</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.3971137586459912</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.2566750929453889</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>5892793.460119134</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2049542.003728769</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>19966662.43242873</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>13829672.94267023</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Turnkey</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2039</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>12</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I15" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>17403261.51973827</v>
+      </c>
+      <c r="L15" t="n">
+        <v>17055196.28934351</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1928767.38696786</v>
+      </c>
+      <c r="N15" t="n">
+        <v>15126428.90237565</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1300326.780812741</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5553763.172801666</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6854089.953614406</v>
+      </c>
+      <c r="U15" t="n">
+        <v>18526362.39780464</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>15126428.90237565</v>
+      </c>
+      <c r="X15" t="n">
+        <v>8272338.94876124</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.206920102412566</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.367697924672214</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.2291741901298115</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>5561956.515105321</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1895806.579061653</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>35093091.33480437</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>22102011.89143147</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Turnkey</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>13</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>17751326.75013304</v>
+      </c>
+      <c r="L16" t="n">
+        <v>17396300.21513038</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1976986.571642057</v>
+      </c>
+      <c r="N16" t="n">
+        <v>15419313.64348832</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1000423.569481451</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5853666.384132955</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6854089.953614406</v>
+      </c>
+      <c r="U16" t="n">
+        <v>12672696.01367169</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15419313.64348832</v>
+      </c>
+      <c r="X16" t="n">
+        <v>8565223.689873915</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.249651485148246</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.3404610413631611</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.2046198126159031</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>5249675.580167232</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1752614.466435295</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>50512404.97829269</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>30667235.58130539</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Turnkey</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2041</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>18106353.2851357</v>
+      </c>
+      <c r="L17" t="n">
+        <v>17744226.21943298</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2026411.235933108</v>
+      </c>
+      <c r="N17" t="n">
+        <v>15717814.98349988</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>684325.5847382711</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6169764.368876135</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6854089.953614406</v>
+      </c>
+      <c r="U17" t="n">
+        <v>6502931.64479555</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>15717814.98349988</v>
+      </c>
+      <c r="X17" t="n">
+        <v>8863725.029885469</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.293202320055824</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.3152417049658899</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.1826962612641992</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>4954910.793736912</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1619369.423833977</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>66230219.96179257</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>39530960.61119086</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Turnkey</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2042</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>18468480.35083841</v>
+      </c>
+      <c r="L18" t="n">
+        <v>18099110.74382164</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2077071.516831435</v>
+      </c>
+      <c r="N18" t="n">
+        <v>16022039.22699021</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>351158.3088189597</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6502931.644795447</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6854089.953614406</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.033768057823181e-07</v>
+      </c>
+      <c r="V18" t="n">
+        <v>245634703.5953456</v>
+      </c>
+      <c r="W18" t="n">
+        <v>261656742.8223358</v>
+      </c>
+      <c r="X18" t="n">
+        <v>254802652.8687213</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.33758811679167</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.2918904675610092</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.163121661843035</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>76375109.00290234</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>41563832.17795978</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>327886962.7841284</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>294333613.4799122</v>
       </c>
     </row>
   </sheetData>
@@ -2301,7 +2796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE13"/>
+  <dimension ref="A1:AE18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2637,16 +3132,16 @@
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9174311926605504</v>
+        <v>0.9259259259259258</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8849557522123894</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="AB3" t="n">
-        <v>-20917431.19266055</v>
+        <v>-21111111.11111111</v>
       </c>
       <c r="AC3" t="n">
-        <v>-8070796.460176991</v>
+        <v>-8142857.142857143</v>
       </c>
       <c r="AD3" t="n">
         <v>-57000000</v>
@@ -2736,16 +3231,16 @@
         <v>0.3517239255768159</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.84167999326656</v>
+        <v>0.8573388203017832</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7831466833737961</v>
+        <v>0.7971938775510203</v>
       </c>
       <c r="AB4" t="n">
-        <v>1049271.946805825</v>
+        <v>1068792.866941015</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1799460.229753775</v>
+        <v>-1831736.90001004</v>
       </c>
       <c r="AD4" t="n">
         <v>-55753360</v>
@@ -2835,16 +3330,16 @@
         <v>0.8747350103833194</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7721834800610642</v>
+        <v>0.7938322410201696</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.6930501622776957</v>
+        <v>0.7117802478134109</v>
       </c>
       <c r="AB5" t="n">
-        <v>2394066.233265819</v>
+        <v>2461185.731341767</v>
       </c>
       <c r="AC5" t="n">
-        <v>-307704.2695165314</v>
+        <v>-316020.1571700432</v>
       </c>
       <c r="AD5" t="n">
         <v>-52652974.8</v>
@@ -2934,16 +3429,16 @@
         <v>1.330599986156647</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7084252110651963</v>
+        <v>0.7350298527964533</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6133187276793768</v>
+        <v>0.6355180784048311</v>
       </c>
       <c r="AB6" t="n">
-        <v>3341032.2581349</v>
+        <v>3466503.46504833</v>
       </c>
       <c r="AC6" t="n">
-        <v>718667.8272133493</v>
+        <v>744680.3365847402</v>
       </c>
       <c r="AD6" t="n">
         <v>-47936835.106</v>
@@ -3033,16 +3528,16 @@
         <v>1.624986992085904</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6499313862983452</v>
+        <v>0.6805831970337529</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5427599359994485</v>
+        <v>0.5674268557185992</v>
       </c>
       <c r="AB7" t="n">
-        <v>3743316.470387549</v>
+        <v>3919857.302838412</v>
       </c>
       <c r="AC7" t="n">
-        <v>1202314.007909373</v>
+        <v>1256955.813877787</v>
       </c>
       <c r="AD7" t="n">
         <v>-42177278.71389</v>
@@ -3132,16 +3627,16 @@
         <v>1.79340319420159</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5962673268792158</v>
+        <v>0.6301696268831045</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.4803185274331404</v>
+        <v>0.5066311211773206</v>
       </c>
       <c r="AB8" t="n">
-        <v>3790164.829488455</v>
+        <v>4005664.319936863</v>
       </c>
       <c r="AC8" t="n">
-        <v>1350710.978169476</v>
+        <v>1424705.020048955</v>
       </c>
       <c r="AD8" t="n">
         <v>-35820792.85824925</v>
@@ -3231,16 +3726,16 @@
         <v>1.89792364318191</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.5470342448433172</v>
+        <v>0.5834903952621338</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.4250606437461419</v>
+        <v>0.4523492153368934</v>
       </c>
       <c r="AB9" t="n">
-        <v>3679869.321721048</v>
+        <v>3925107.843402036</v>
       </c>
       <c r="AC9" t="n">
-        <v>1352787.085925</v>
+        <v>1439634.992887084</v>
       </c>
       <c r="AD9" t="n">
         <v>-29093847.77864999</v>
@@ -3330,16 +3825,16 @@
         <v>1.982109108016156</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.501866279672768</v>
+        <v>0.5402688845019757</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.3761598617222495</v>
+        <v>0.403883227979369</v>
       </c>
       <c r="AB10" t="n">
-        <v>3525776.019887731</v>
+        <v>3795566.97555092</v>
       </c>
       <c r="AC10" t="n">
-        <v>1309396.985692285</v>
+        <v>1405900.88178612</v>
       </c>
       <c r="AD10" t="n">
         <v>-22068518.19845456</v>
@@ -3429,16 +3924,16 @@
         <v>2.020360719790115</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.4604277795163009</v>
+        <v>0.5002489671314589</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.3328848333825217</v>
+        <v>0.3606100249815795</v>
       </c>
       <c r="AB11" t="n">
-        <v>3297080.727930925</v>
+        <v>3582236.567978606</v>
       </c>
       <c r="AC11" t="n">
-        <v>1203890.219264404</v>
+        <v>1304159.392402076</v>
       </c>
       <c r="AD11" t="n">
         <v>-14907610.72368262</v>
@@ -3528,16 +4023,16 @@
         <v>2.059342599539895</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.4224108068956888</v>
+        <v>0.4631934880846841</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.2945883481261255</v>
+        <v>0.3219732365906959</v>
       </c>
       <c r="AB12" t="n">
-        <v>3083207.615353763</v>
+        <v>3380883.411436096</v>
       </c>
       <c r="AC12" t="n">
-        <v>1106091.737518202</v>
+        <v>1208913.858814562</v>
       </c>
       <c r="AD12" t="n">
         <v>-7608537.013868327</v>
@@ -3615,34 +4110,529 @@
         <v>14889650.34418355</v>
       </c>
       <c r="V13" t="n">
-        <v>101111557.9134374</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>108551434.8851335</v>
+        <v>7439876.971696155</v>
       </c>
       <c r="X13" t="n">
-        <v>90117413.77357738</v>
+        <v>3895506.20432356</v>
       </c>
       <c r="Y13" t="n">
         <v>2.099068483518517</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.3875328503630173</v>
+        <v>0.4288828593376705</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.2606976532089606</v>
+        <v>0.2874761040988356</v>
       </c>
       <c r="AB13" t="n">
-        <v>42067246.97203127</v>
+        <v>3190835.708741536</v>
       </c>
       <c r="AC13" t="n">
-        <v>23493398.28403249</v>
+        <v>1119864.94711178</v>
       </c>
       <c r="AD13" t="n">
-        <v>100942897.8712652</v>
+        <v>-168660.0421721721</v>
       </c>
       <c r="AE13" t="n">
-        <v>84809539.85335571</v>
+        <v>-1412367.715898117</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Powered Shell</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2038</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>52</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9127830.216920743</v>
+      </c>
+      <c r="L14" t="n">
+        <v>8671438.706074705</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1088071.862566903</v>
+      </c>
+      <c r="N14" t="n">
+        <v>7583366.843507802</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>908268.6709951962</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2636102.096377398</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3544370.767372595</v>
+      </c>
+      <c r="U14" t="n">
+        <v>12253548.24780615</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>7583366.843507802</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4038996.076135207</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.139552360976409</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.3971137586459912</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.2566750929453889</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3011459.310416769</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1036709.693248065</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>7414706.80133563</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2626628.360237091</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Powered Shell</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2039</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>12</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I15" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>52</v>
+      </c>
+      <c r="K15" t="n">
+        <v>9310386.821259158</v>
+      </c>
+      <c r="L15" t="n">
+        <v>8844867.4801962</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1115273.659131076</v>
+      </c>
+      <c r="N15" t="n">
+        <v>7729593.821065124</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>747466.4431161749</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2796904.32425642</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3544370.767372595</v>
+      </c>
+      <c r="U15" t="n">
+        <v>9456643.923549727</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>7729593.821065124</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4185223.053692529</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.180808478678147</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.367697924672214</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.2291741901298115</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2842155.606564815</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>959145.103842602</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15144300.62240075</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>6811851.413929621</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Powered Shell</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>13</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>52</v>
+      </c>
+      <c r="K16" t="n">
+        <v>9496594.557684341</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9021764.829800123</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1143155.500609352</v>
+      </c>
+      <c r="N16" t="n">
+        <v>7878609.329190771</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>576855.2793365333</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2967515.488036062</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3544370.767372595</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6489128.435513665</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>7878609.329190771</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4334238.561818176</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.222851345495974</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.3404610413631611</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.2046198126159031</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2682359.536709806</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>886871.0823518566</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>23022909.95159153</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>11146089.9757478</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Powered Shell</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2041</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>52</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9686526.448838029</v>
+      </c>
+      <c r="L17" t="n">
+        <v>9202200.126396127</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1171734.388124586</v>
+      </c>
+      <c r="N17" t="n">
+        <v>8030465.738271541</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>395836.8345663336</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3148533.932806261</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3544370.767372594</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3340594.502707404</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>8030465.738271541</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4486094.970898947</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.265695737081266</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.3152417049658899</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.1826962612641992</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2531537.711002884</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>819592.778859364</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>31053375.68986307</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>15632184.94664674</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Powered Shell</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2042</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>52</v>
+      </c>
+      <c r="K18" t="n">
+        <v>9880256.977814788</v>
+      </c>
+      <c r="L18" t="n">
+        <v>9386244.128924048</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1201027.747827701</v>
+      </c>
+      <c r="N18" t="n">
+        <v>8185216.381096346</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>203776.2646651517</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3340594.502707404</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3544370.767372556</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>104564541.8104052</v>
+      </c>
+      <c r="W18" t="n">
+        <v>112749758.1915015</v>
+      </c>
+      <c r="X18" t="n">
+        <v>109205387.424129</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.309356700615171</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.2918904675610092</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.163121661843035</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>32910579.6359081</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>17813764.27883639</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>143803133.8813646</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>124837572.3707757</v>
       </c>
     </row>
   </sheetData>
@@ -3656,7 +4646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE13"/>
+  <dimension ref="A1:AE18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3992,16 +4982,16 @@
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9174311926605504</v>
+        <v>0.9259259259259258</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8849557522123894</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="AB3" t="n">
-        <v>-22590825.6880734</v>
+        <v>-22800000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-8716460.176991154</v>
+        <v>-8794285.714285716</v>
       </c>
       <c r="AD3" t="n">
         <v>-61560000</v>
@@ -4091,16 +5081,16 @@
         <v>0.1482881492962099</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.84167999326656</v>
+        <v>0.8573388203017832</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7831466833737961</v>
+        <v>0.7971938775510203</v>
       </c>
       <c r="AB4" t="n">
-        <v>502963.7235922902</v>
+        <v>512320.987654321</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2687936.573121438</v>
+        <v>-2736149.72115654</v>
       </c>
       <c r="AD4" t="n">
         <v>-60962428.8</v>
@@ -4190,16 +5180,16 @@
         <v>0.568601792782335</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7721834800610642</v>
+        <v>0.7938322410201696</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.6930501622776957</v>
+        <v>0.7117802478134109</v>
       </c>
       <c r="AB5" t="n">
-        <v>1769342.641747791</v>
+        <v>1818947.530864197</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1204831.237585749</v>
+        <v>-1237392.505679126</v>
       </c>
       <c r="AD5" t="n">
         <v>-58671078.768</v>
@@ -4289,16 +5279,16 @@
         <v>0.9345201994250029</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7084252110651963</v>
+        <v>0.7350298527964533</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6133187276793768</v>
+        <v>0.6355180784048311</v>
       </c>
       <c r="AB6" t="n">
-        <v>2667877.68610842</v>
+        <v>2768068.82684296</v>
       </c>
       <c r="AC6" t="n">
-        <v>-161836.6155455682</v>
+        <v>-167694.3655645676</v>
       </c>
       <c r="AD6" t="n">
         <v>-54905151.68856</v>
@@ -4388,16 +5378,16 @@
         <v>1.169710808778477</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6499313862983452</v>
+        <v>0.6805831970337529</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5427599359994485</v>
+        <v>0.5674268557185992</v>
       </c>
       <c r="AB7" t="n">
-        <v>3063580.007908273</v>
+        <v>3208063.374237156</v>
       </c>
       <c r="AC7" t="n">
-        <v>371193.616679352</v>
+        <v>388063.3274586312</v>
       </c>
       <c r="AD7" t="n">
         <v>-50191454.1006396</v>
@@ -4487,16 +5477,16 @@
         <v>1.302903840667823</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5962673268792158</v>
+        <v>0.6301696268831045</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.4803185274331404</v>
+        <v>0.5066311211773206</v>
       </c>
       <c r="AB8" t="n">
-        <v>3130664.942985653</v>
+        <v>3308666.884940552</v>
       </c>
       <c r="AC8" t="n">
-        <v>586296.5417612889</v>
+        <v>618414.7754663796</v>
       </c>
       <c r="AD8" t="n">
         <v>-44941015.57775232</v>
@@ -4586,16 +5576,16 @@
         <v>1.384327617247288</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.5470342448433172</v>
+        <v>0.5834903952621338</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.4250606437461419</v>
+        <v>0.4523492153368934</v>
       </c>
       <c r="AB9" t="n">
-        <v>3051663.273149848</v>
+        <v>3255036.090047982</v>
       </c>
       <c r="AC9" t="n">
-        <v>658317.9583359769</v>
+        <v>700581.4729658037</v>
       </c>
       <c r="AD9" t="n">
         <v>-39362455.73087489</v>
@@ -4685,16 +5675,16 @@
         <v>1.449229090897905</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.501866279672768</v>
+        <v>0.5402688845019757</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.3761598617222495</v>
+        <v>0.403883227979369</v>
       </c>
       <c r="AB10" t="n">
-        <v>2930949.077897094</v>
+        <v>3155224.116432066</v>
       </c>
       <c r="AC10" t="n">
-        <v>680963.0354196506</v>
+        <v>731150.707097493</v>
       </c>
       <c r="AD10" t="n">
         <v>-33522356.09356082</v>
@@ -4784,16 +5774,16 @@
         <v>1.476892764429977</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.4604277795163009</v>
+        <v>0.5002489671314589</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.3328848333825217</v>
+        <v>0.3606100249815795</v>
       </c>
       <c r="AB11" t="n">
-        <v>2740272.136575225</v>
+        <v>2977271.066096351</v>
       </c>
       <c r="AC11" t="n">
-        <v>639731.8235648599</v>
+        <v>693013.5762963486</v>
       </c>
       <c r="AD11" t="n">
         <v>-27570777.45629007</v>
@@ -4883,16 +5873,16 @@
         <v>1.505076688725545</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.4224108068956888</v>
+        <v>0.4631934880846841</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.2945883481261255</v>
+        <v>0.3219732365906959</v>
       </c>
       <c r="AB12" t="n">
-        <v>2561986.6552408</v>
+        <v>2809339.902992692</v>
       </c>
       <c r="AC12" t="n">
-        <v>599592.3775826722</v>
+        <v>655330.394679255</v>
       </c>
       <c r="AD12" t="n">
         <v>-21505623.31388323</v>
@@ -4970,34 +5960,529 @@
         <v>16567300.06091334</v>
       </c>
       <c r="V13" t="n">
-        <v>76348482.06112058</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>82529346.81707598</v>
+        <v>6180864.755955399</v>
       </c>
       <c r="X13" t="n">
-        <v>61932249.34594388</v>
+        <v>2151067.345736635</v>
       </c>
       <c r="Y13" t="n">
         <v>1.533790443232197</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.3875328503630173</v>
+        <v>0.4288828593376705</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.2606976532089606</v>
+        <v>0.2874761040988356</v>
       </c>
       <c r="AB13" t="n">
-        <v>31982833.01061947</v>
+        <v>2650866.949713585</v>
       </c>
       <c r="AC13" t="n">
-        <v>16145592.06243975</v>
+        <v>618380.4602065908</v>
       </c>
       <c r="AD13" t="n">
-        <v>61023723.50319275</v>
+        <v>-15324758.55792784</v>
       </c>
       <c r="AE13" t="n">
-        <v>41094449.34009176</v>
+        <v>-18686732.66011548</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Powered Shell</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2038</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8397603.799567083</v>
+      </c>
+      <c r="L14" t="n">
+        <v>7473867.381614703</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1175117.611572256</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6298749.770042447</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1143143.704203021</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2886653.706015743</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4029797.410218764</v>
+      </c>
+      <c r="U14" t="n">
+        <v>13680646.3548976</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>6298749.770042447</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2268952.359823683</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.563043778347287</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.3971137586459912</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.2566750929453889</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2501320.195952129</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>582383.5578464033</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-9026008.787885388</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-16417780.3002918</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Powered Shell</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2039</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>12</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="I15" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8565555.875558425</v>
+      </c>
+      <c r="L15" t="n">
+        <v>7623344.729246997</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1204495.551861562</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6418849.177385435</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>943964.5984879343</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3085832.81173083</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4029797.410218764</v>
+      </c>
+      <c r="U15" t="n">
+        <v>10594813.54316677</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>6418849.177385435</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2389051.767166671</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.592846618320939</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.367697924672214</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.2291741901298115</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2360197.521308573</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>547509.0039186169</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-2607159.610499953</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-14028728.53312513</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Powered Shell</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>13</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="I16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8736866.993069593</v>
+      </c>
+      <c r="L16" t="n">
+        <v>7775811.623831937</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1234607.940658101</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6541203.683173836</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>731042.1344785071</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3298755.275740257</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4029797.410218764</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7296058.267426511</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>6541203.683173836</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2511406.272955072</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.623209064204232</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.3404610413631611</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.2046198126159031</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2227025.017741909</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>513883.4809744705</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3934044.072673883</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-11517322.26017006</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Powered Shell</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2041</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8911604.332930986</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7931327.856308577</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1265473.139174553</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6665854.717134023</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>503428.0204524293</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3526369.389766335</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4029797.410218764</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3769688.877660177</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>6665854.717134023</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2636057.306915259</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.654141396843112</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.3152417049658899</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.1826962612641992</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2101355.406084249</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>481597.8144515915</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>10599898.78980791</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-8881264.953254798</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Powered Shell</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2042</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="K18" t="n">
+        <v>9089836.419589605</v>
+      </c>
+      <c r="L18" t="n">
+        <v>8089954.413434748</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1297109.967653917</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6792844.44578083</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>260108.5325585522</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3769688.877660177</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4029797.410218729</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>78871307.12444469</v>
+      </c>
+      <c r="W18" t="n">
+        <v>85664151.57022552</v>
+      </c>
+      <c r="X18" t="n">
+        <v>81634354.16000679</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.685654079918655</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.2918904675610092</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.163121661843035</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>25004549.25505029</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>13316331.51406318</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>96264050.36003342</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>72753089.20675199</v>
       </c>
     </row>
   </sheetData>
@@ -5011,7 +6496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE13"/>
+  <dimension ref="A1:AE18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5347,16 +6832,16 @@
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9174311926605504</v>
+        <v>0.9259259259259258</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8849557522123894</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="AB3" t="n">
-        <v>-20289908.25688073</v>
+        <v>-20477777.77777778</v>
       </c>
       <c r="AC3" t="n">
-        <v>-7828672.566371682</v>
+        <v>-7898571.428571428</v>
       </c>
       <c r="AD3" t="n">
         <v>-55290000</v>
@@ -5446,16 +6931,16 @@
         <v>0.4998380009649149</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.84167999326656</v>
+        <v>0.8573388203017832</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7831466833737961</v>
+        <v>0.7971938775510203</v>
       </c>
       <c r="AB4" t="n">
-        <v>1408957.49516034</v>
+        <v>1435170.096021948</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1311823.545853138</v>
+        <v>-1335353.544084718</v>
       </c>
       <c r="AD4" t="n">
         <v>-53616017.6</v>
@@ -5545,16 +7030,16 @@
         <v>1.099716207789583</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7721834800610642</v>
+        <v>0.7938322410201696</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.6930501622776957</v>
+        <v>0.7117802478134109</v>
       </c>
       <c r="AB5" t="n">
-        <v>2843955.185559551</v>
+        <v>2923687.668292435</v>
       </c>
       <c r="AC5" t="n">
-        <v>231447.2580510799</v>
+        <v>237702.255418163</v>
       </c>
       <c r="AD5" t="n">
         <v>-49933013.16</v>
@@ -5644,16 +7129,16 @@
         <v>1.622892125377877</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7084252110651963</v>
+        <v>0.7350298527964533</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6133187276793768</v>
+        <v>0.6355180784048311</v>
       </c>
       <c r="AB6" t="n">
-        <v>3850394.938908277</v>
+        <v>3994995.06927274</v>
       </c>
       <c r="AC6" t="n">
-        <v>1279442.235989412</v>
+        <v>1325752.230528722</v>
       </c>
       <c r="AD6" t="n">
         <v>-44497866.473</v>
@@ -5743,16 +7228,16 @@
         <v>1.961546640730486</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6499313862983452</v>
+        <v>0.6805831970337529</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5427599359994485</v>
+        <v>0.5674268557185992</v>
       </c>
       <c r="AB7" t="n">
-        <v>4269605.664212058</v>
+        <v>4470967.142505364</v>
       </c>
       <c r="AC7" t="n">
-        <v>1747832.272968763</v>
+        <v>1827266.35699059</v>
       </c>
       <c r="AD7" t="n">
         <v>-37928548.9200666</v>
@@ -5842,16 +7327,16 @@
         <v>2.156264980072765</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5962673268792158</v>
+        <v>0.6301696268831045</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.4803185274331404</v>
+        <v>0.5066311211773206</v>
       </c>
       <c r="AB8" t="n">
-        <v>4305908.119837913</v>
+        <v>4550731.510768901</v>
       </c>
       <c r="AC8" t="n">
-        <v>1859980.229848636</v>
+        <v>1961872.831039263</v>
       </c>
       <c r="AD8" t="n">
         <v>-30707109.93501528</v>
@@ -5941,16 +7426,16 @@
         <v>2.277999137964441</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.5470342448433172</v>
+        <v>0.5834903952621338</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.4250606437461419</v>
+        <v>0.4523492153368934</v>
       </c>
       <c r="AB9" t="n">
-        <v>4173396.874141206</v>
+        <v>4451525.685335995</v>
       </c>
       <c r="AC9" t="n">
-        <v>1819294.778701695</v>
+        <v>1936092.126430109</v>
       </c>
       <c r="AD9" t="n">
         <v>-23077977.18239106</v>
@@ -6040,16 +7525,16 @@
         <v>2.376539548448211</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.501866279672768</v>
+        <v>0.5402688845019757</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.3761598617222495</v>
+        <v>0.403883227979369</v>
       </c>
       <c r="AB10" t="n">
-        <v>3994428.750475994</v>
+        <v>4300080.823619811</v>
       </c>
       <c r="AC10" t="n">
-        <v>1734134.434603908</v>
+        <v>1861941.914778668</v>
       </c>
       <c r="AD10" t="n">
         <v>-15118827.67929935</v>
@@ -6139,16 +7624,16 @@
         <v>2.422628102588312</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.4604277795163009</v>
+        <v>0.5002489671314589</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.3328848333825217</v>
+        <v>0.3606100249815795</v>
       </c>
       <c r="AB11" t="n">
-        <v>3735681.880350048</v>
+        <v>4058771.180444503</v>
       </c>
       <c r="AC11" t="n">
-        <v>1586013.971417388</v>
+        <v>1718109.329411064</v>
       </c>
       <c r="AD11" t="n">
         <v>-7005325.309232669</v>
@@ -6238,16 +7723,16 @@
         <v>2.469602371890494</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.4224108068956888</v>
+        <v>0.4631934880846841</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.2945883481261255</v>
+        <v>0.3219732365906959</v>
       </c>
       <c r="AB12" t="n">
-        <v>3493684.400952464</v>
+        <v>3830990.679042539</v>
       </c>
       <c r="AC12" t="n">
-        <v>1449896.581878403</v>
+        <v>1584678.749715206</v>
       </c>
       <c r="AD12" t="n">
         <v>1265496.232071321</v>
@@ -6325,34 +7810,529 @@
         <v>14223299.70655135</v>
       </c>
       <c r="V13" t="n">
-        <v>122779786.803905</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>131210950.127967</v>
+        <v>8431163.324061941</v>
       </c>
       <c r="X13" t="n">
-        <v>113638600.5357157</v>
+        <v>5082113.438362069</v>
       </c>
       <c r="Y13" t="n">
         <v>2.517479169259979</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.3875328503630173</v>
+        <v>0.4288828593376705</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.2606976532089606</v>
+        <v>0.2874761040988356</v>
       </c>
       <c r="AB13" t="n">
-        <v>50848553.50193074</v>
+        <v>3615981.433966584</v>
       </c>
       <c r="AC13" t="n">
-        <v>29625316.47361162</v>
+        <v>1460986.171848666</v>
       </c>
       <c r="AD13" t="n">
-        <v>132476446.3600383</v>
+        <v>9696659.556133263</v>
       </c>
       <c r="AE13" t="n">
-        <v>117936647.7964882</v>
+        <v>9380160.699134553</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Powered Shell</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2038</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>56.16</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9858056.634274403</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9660895.501588915</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1066310.425315565</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8594585.07627335</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>810728.0832734269</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2538321.802426444</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3349049.885699871</v>
+      </c>
+      <c r="U14" t="n">
+        <v>11684977.90412491</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>8594585.07627335</v>
+      </c>
+      <c r="X14" t="n">
+        <v>5245535.190573479</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.566275621325147</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.3971137586459912</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.2566750929453889</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3413027.983641653</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1346398.232588756</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>18291244.63240661</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>14625695.88970803</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Powered Shell</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2039</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>12</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I15" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>56.16</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10055217.76695989</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9854113.411620693</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1092968.185948454</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8761145.225672239</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>666043.7405351195</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2683006.145164752</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3349049.885699871</v>
+      </c>
+      <c r="U15" t="n">
+        <v>9001971.758960154</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>8761145.225672239</v>
+      </c>
+      <c r="X15" t="n">
+        <v>5412095.339972368</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.616009174148616</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.367697924672214</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.2291741901298115</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3221454.917231558</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1240312.566443494</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>27052389.85807885</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>20037791.2296804</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Powered Shell</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>13</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>56.16</v>
+      </c>
+      <c r="K16" t="n">
+        <v>10256322.12229909</v>
+      </c>
+      <c r="L16" t="n">
+        <v>10051195.67985311</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1120292.390597166</v>
+      </c>
+      <c r="N16" t="n">
+        <v>8930903.289255939</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>513112.3902607287</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2835937.495439143</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3349049.885699871</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6166034.263521011</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>8930903.289255939</v>
+      </c>
+      <c r="X16" t="n">
+        <v>5581853.403556067</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.666697599038479</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.3404610413631611</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.2046198126159031</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3040624.634173758</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1142157.797485084</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>35983293.14733479</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>25619644.63323646</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Powered Shell</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2041</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>56.16</v>
+      </c>
+      <c r="K17" t="n">
+        <v>10461448.56474507</v>
+      </c>
+      <c r="L17" t="n">
+        <v>10252219.59345017</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1148299.700362094</v>
+      </c>
+      <c r="N17" t="n">
+        <v>9103919.893088074</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>351463.9530206976</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2997585.932679174</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3349049.885699871</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3168448.330841837</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>9103919.893088074</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5754870.007388202</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.718358998461312</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.3152417049658899</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.1826962612641992</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2869935.228969967</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1051393.234411299</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>45087213.04042286</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>31374514.64062466</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Powered Shell</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2042</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>56.16</v>
+      </c>
+      <c r="K18" t="n">
+        <v>10670677.53603997</v>
+      </c>
+      <c r="L18" t="n">
+        <v>10457263.98531917</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1177007.192871147</v>
+      </c>
+      <c r="N18" t="n">
+        <v>9280256.792448025</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>180601.5548579847</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3168448.330841837</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3349049.885699822</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>127033975.4113239</v>
+      </c>
+      <c r="W18" t="n">
+        <v>136314232.2037719</v>
+      </c>
+      <c r="X18" t="n">
+        <v>132965182.3180721</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.771011812058694</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.2918904675610092</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.163121661843035</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>39788824.97317896</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>21689501.50698605</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>181401445.2441948</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>164339696.9586968</v>
       </c>
     </row>
   </sheetData>
@@ -6366,7 +8346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE7"/>
+  <dimension ref="A1:AE18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6702,16 +8682,16 @@
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9174311926605504</v>
+        <v>0.9259259259259258</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8849557522123894</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="AB3" t="n">
-        <v>-22752293.57798165</v>
+        <v>-22962962.96296296</v>
       </c>
       <c r="AC3" t="n">
-        <v>-8778761.061946902</v>
+        <v>-8857142.857142856</v>
       </c>
       <c r="AD3" t="n">
         <v>-62000000</v>
@@ -6801,16 +8781,16 @@
         <v>0.3897511735712555</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.84167999326656</v>
+        <v>0.8573388203017832</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7831466833737961</v>
+        <v>0.7971938775510203</v>
       </c>
       <c r="AB4" t="n">
-        <v>1272956.821816345</v>
+        <v>1296639.231824417</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1854510.527637129</v>
+        <v>-1887774.627503068</v>
       </c>
       <c r="AD4" t="n">
         <v>-60487600</v>
@@ -6900,16 +8880,16 @@
         <v>1.000432506099086</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7721834800610642</v>
+        <v>0.7938322410201696</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.6930501622776957</v>
+        <v>0.7117802478134109</v>
       </c>
       <c r="AB5" t="n">
-        <v>2997695.650058801</v>
+        <v>3081738.365594675</v>
       </c>
       <c r="AC5" t="n">
-        <v>1163.151118999177</v>
+        <v>1194.585957537009</v>
       </c>
       <c r="AD5" t="n">
         <v>-56605497.2</v>
@@ -6999,16 +8979,16 @@
         <v>1.503337797427693</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7084252110651963</v>
+        <v>0.7350298527964533</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6133187276793768</v>
+        <v>0.6355180784048311</v>
       </c>
       <c r="AB6" t="n">
-        <v>4132661.383991817</v>
+        <v>4287861.924289336</v>
       </c>
       <c r="AC6" t="n">
-        <v>1197912.254010754</v>
+        <v>1241271.233714055</v>
       </c>
       <c r="AD6" t="n">
         <v>-50771908.39</v>
@@ -7086,34 +9066,1123 @@
         <v>30293787.5830317</v>
       </c>
       <c r="V7" t="n">
-        <v>95827870.43114829</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>102644180.0749983</v>
+        <v>6816309.643850001</v>
       </c>
       <c r="X7" t="n">
-        <v>68469967.99922675</v>
+        <v>2935885.151110151</v>
       </c>
       <c r="Y7" t="n">
         <v>1.756588655855332</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6499313862983452</v>
+        <v>0.6805831970337529</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5427599359994485</v>
+        <v>0.5674268557185992</v>
       </c>
       <c r="AB7" t="n">
-        <v>66711674.25160062</v>
+        <v>4639065.809383435</v>
       </c>
       <c r="AC7" t="n">
-        <v>37162755.44914459</v>
+        <v>1665900.080045358</v>
       </c>
       <c r="AD7" t="n">
-        <v>51872271.68499829</v>
+        <v>-43955598.74615</v>
       </c>
       <c r="AE7" t="n">
-        <v>43256786.1310072</v>
+        <v>-22277296.7171094</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2032</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>57</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8884603.16928</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7996142.852352</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1048622.24609375</v>
+      </c>
+      <c r="N8" t="n">
+        <v>6947520.606258251</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1878214.830147966</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2002209.662591884</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3880424.492739849</v>
+      </c>
+      <c r="U8" t="n">
+        <v>28291577.92043982</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>6947520.606258251</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3067096.113518402</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.790402214823878</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.6301696268831045</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.5066311211773206</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4378116.468208442</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1553886.34275043</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-37008078.13989175</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-19210200.603591</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2033</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>57</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9062295.2326656</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8156065.709399041</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1074837.802246093</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7081227.907152947</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1754077.831067269</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2126346.66167258</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3880424.492739849</v>
+      </c>
+      <c r="U9" t="n">
+        <v>26165231.25876724</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>7081227.907152947</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3200803.414413098</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.824859089618082</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.5834903952621338</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.4523492153368934</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>4131828.470485925</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1447880.912957414</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-29926850.2327388</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-16009397.1891779</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2034</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>57</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9243541.137318913</v>
+      </c>
+      <c r="L10" t="n">
+        <v>8319187.023587022</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1101708.747302245</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7217478.276284777</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1622244.338043569</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2258180.15469628</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3880424.492739849</v>
+      </c>
+      <c r="U10" t="n">
+        <v>23907051.10407096</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>7217478.276284777</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3337053.783544928</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.859971322670612</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.5402688845019757</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.403883227979369</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3899378.937245619</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1347780.054038892</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-22709371.95645403</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-12672343.40563297</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2035</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>57</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9428411.96006529</v>
+      </c>
+      <c r="L11" t="n">
+        <v>8485570.764058761</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1129251.465984802</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7356319.29807396</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1482237.1684524</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2398187.32428745</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3880424.49273985</v>
+      </c>
+      <c r="U11" t="n">
+        <v>21508863.77978351</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>7356319.29807396</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3475894.80533411</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.895751176665697</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.5002489671314589</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.3606100249815795</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3679991.130750717</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1253442.512584876</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-15353052.65838007</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-9196448.600298859</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2036</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>57</v>
+      </c>
+      <c r="K12" t="n">
+        <v>9616980.199266598</v>
+      </c>
+      <c r="L12" t="n">
+        <v>8655282.179339938</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1157482.752634421</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7497799.426705517</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1333549.554346577</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2546874.938393272</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3880424.492739849</v>
+      </c>
+      <c r="U12" t="n">
+        <v>18961988.84139024</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>7497799.426705517</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3617374.933965668</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.932211138429226</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.4631934880846841</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.3219732365906959</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3472931.869415073</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1164697.915450981</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-7855253.231674552</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-5579073.666333191</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2037</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>57</v>
+      </c>
+      <c r="K13" t="n">
+        <v>9809319.80325193</v>
+      </c>
+      <c r="L13" t="n">
+        <v>8828387.822926737</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1186419.821450282</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7641968.001476455</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1175643.308166195</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2704781.184573655</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3880424.492739849</v>
+      </c>
+      <c r="U13" t="n">
+        <v>16257207.65681658</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>7641968.001476455</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3761543.508736606</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.969363922883781</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.4288828593376705</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.2874761040988356</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3277509.087440206</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1081353.873289864</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-213285.2301980965</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-1817530.157596585</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2038</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>57</v>
+      </c>
+      <c r="K14" t="n">
+        <v>10005506.19931697</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9004955.579385271</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1216080.316986539</v>
+      </c>
+      <c r="N14" t="n">
+        <v>7788875.262398733</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1007946.874722628</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2872477.618017221</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3880424.492739849</v>
+      </c>
+      <c r="U14" t="n">
+        <v>13384730.03879936</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>7788875.262398733</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3908450.769658884</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.007222477069576</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.3971137586459912</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.2566750929453889</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3093069.531075942</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1003201.964574671</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>7575590.032200636</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2090920.612062299</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2039</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>12</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I15" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>57</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10205616.32330331</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9185054.690972976</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1246482.324911202</v>
+      </c>
+      <c r="N15" t="n">
+        <v>7938572.366061774</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>829853.2624055605</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3050571.230334289</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3880424.492739849</v>
+      </c>
+      <c r="U15" t="n">
+        <v>10334158.80846507</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>7938572.366061774</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4058147.873321925</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.04579998423229</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.367697924672214</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.2291741901298115</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2918996.583861102</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>930022.7522955689</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15514162.39826241</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>6149068.485384224</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>13</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>57</v>
+      </c>
+      <c r="K16" t="n">
+        <v>10409728.64976937</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9368755.784792436</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1277644.383033982</v>
+      </c>
+      <c r="N16" t="n">
+        <v>8091111.401758454</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>640717.8461248345</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3239706.646615015</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3880424.492739849</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7094452.161850058</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>8091111.401758454</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4210686.909018604</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.085109867978791</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.3404610413631611</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.2046198126159031</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2754708.213628029</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>861589.9663076231</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>23605273.80002087</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>10359755.39440283</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2041</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>57</v>
+      </c>
+      <c r="K17" t="n">
+        <v>10617923.22276476</v>
+      </c>
+      <c r="L17" t="n">
+        <v>9556130.900488285</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1309585.492609832</v>
+      </c>
+      <c r="N17" t="n">
+        <v>8246545.407878454</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>439856.0340347036</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3440568.458705146</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3880424.492739849</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3653883.703144912</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>8246545.407878454</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4366120.915138604</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.125165796501769</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.3152417049658899</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.1826962612641992</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2599655.034458234</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>797673.9674232468</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>31851819.20789932</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>14725876.30954143</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2042</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>57</v>
+      </c>
+      <c r="K18" t="n">
+        <v>10830281.68722006</v>
+      </c>
+      <c r="L18" t="n">
+        <v>9747253.51849805</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1342325.129925077</v>
+      </c>
+      <c r="N18" t="n">
+        <v>8404928.388572972</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>226540.7895949845</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3653883.703144865</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3880424.492739849</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4.703179001808167e-08</v>
+      </c>
+      <c r="V18" t="n">
+        <v>111066709.1152155</v>
+      </c>
+      <c r="W18" t="n">
+        <v>119471637.5037884</v>
+      </c>
+      <c r="X18" t="n">
+        <v>115591213.0110485</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.165981686874291</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.2918904675610092</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.163121661843035</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>34872632.13126021</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>18855430.76081448</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>151323456.7116878</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>130317089.32059</v>
       </c>
     </row>
   </sheetData>
@@ -7127,7 +10196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE7"/>
+  <dimension ref="A1:AE18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7463,16 +10532,16 @@
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9174311926605504</v>
+        <v>0.9259259259259258</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8849557522123894</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="AB3" t="n">
-        <v>-24572477.06422019</v>
+        <v>-24800000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-9481061.946902659</v>
+        <v>-9565714.285714289</v>
       </c>
       <c r="AD3" t="n">
         <v>-66960000</v>
@@ -7562,16 +10631,16 @@
         <v>0.178260484646233</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.84167999326656</v>
+        <v>0.8573388203017832</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7831466833737961</v>
+        <v>0.7971938775510203</v>
       </c>
       <c r="AB4" t="n">
-        <v>661835.1990573182</v>
+        <v>674148.148148148</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2838736.347394187</v>
+        <v>-2889654.370206981</v>
       </c>
       <c r="AD4" t="n">
         <v>-66173673.6</v>
@@ -7661,16 +10730,16 @@
         <v>0.6695802461018209</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7721834800610642</v>
+        <v>0.7938322410201696</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.6930501622776957</v>
+        <v>0.7117802478134109</v>
       </c>
       <c r="AB5" t="n">
-        <v>2280714.442688156</v>
+        <v>2344656.035665295</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1010132.738502913</v>
+        <v>-1037432.165910023</v>
       </c>
       <c r="AD5" t="n">
         <v>-63220082.256</v>
@@ -7760,16 +10829,16 @@
         <v>1.073612277140287</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7084252110651963</v>
+        <v>0.7350298527964533</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6133187276793768</v>
+        <v>0.6355180784048311</v>
       </c>
       <c r="AB6" t="n">
-        <v>3354974.714186024</v>
+        <v>3480969.524780266</v>
       </c>
       <c r="AC6" t="n">
-        <v>199151.8075366843</v>
+        <v>206360.197927506</v>
       </c>
       <c r="AD6" t="n">
         <v>-58484261.64744</v>
@@ -7847,34 +10916,1123 @@
         <v>33077468.67253888</v>
       </c>
       <c r="V7" t="n">
-        <v>71668866.2929792</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>77295369.9717484</v>
+        <v>5626503.678769202</v>
       </c>
       <c r="X7" t="n">
-        <v>39806792.45722188</v>
+        <v>1215394.836781565</v>
       </c>
       <c r="Y7" t="n">
         <v>1.275530457379036</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6499313862983452</v>
+        <v>0.6805831970337529</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5427599359994485</v>
+        <v>0.5674268557185992</v>
       </c>
       <c r="AB7" t="n">
-        <v>50236686.96018192</v>
+        <v>3829303.861818915</v>
       </c>
       <c r="AC7" t="n">
-        <v>21605532.12642508</v>
+        <v>689647.6706915835</v>
       </c>
       <c r="AD7" t="n">
-        <v>18811108.3243084</v>
+        <v>-52857757.9686708</v>
       </c>
       <c r="AE7" t="n">
-        <v>8265204.283818964</v>
+        <v>-30326193.33662135</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2032</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8173834.9157376</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6866021.329219584</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1132512.02578125</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5733509.303438335</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2315422.807077722</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2095686.034909915</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4411108.841987637</v>
+      </c>
+      <c r="U8" t="n">
+        <v>30981782.63762897</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>5733509.303438335</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1322400.461450698</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.299788671923776</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.6301696268831045</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.5066311211773206</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3613083.418478544</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>669969.2284301731</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-47124248.66523246</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-29003792.87517066</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2033</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8337311.614052352</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7003341.755803977</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1160824.826425781</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5842516.929378197</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2168724.784634028</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2242384.057353609</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4411108.841987637</v>
+      </c>
+      <c r="U9" t="n">
+        <v>28739398.58027536</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>5842516.929378197</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1431408.08739056</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.324500740894339</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.5834903952621338</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.4523492153368934</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3409052.512448592</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>647496.325158003</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-41281731.73585427</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-27572384.78778009</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2034</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="I10" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8504057.846333399</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7143408.590920056</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1189845.447086425</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5953563.143833631</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2011757.900619275</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2399350.941368361</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4411108.841987637</v>
+      </c>
+      <c r="U10" t="n">
+        <v>26340047.638907</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>5953563.143833631</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1542454.301845994</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.349674958632616</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.5402688845019757</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.403883227979369</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3216524.918531071</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>622971.4224402241</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-35328168.59202064</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-26029930.4859341</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2035</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8674139.003260067</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7286276.762738457</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1219591.583263586</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6066685.179474871</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1843803.33472349</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2567305.507264147</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4411108.841987637</v>
+      </c>
+      <c r="U11" t="n">
+        <v>23772742.13164286</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>6066685.179474871</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1655576.337487234</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.375319765798668</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.5002489671314589</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.3606100249815795</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3034852.994944034</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>597017.4244201832</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-29261483.41254577</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-24374354.14844687</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2036</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8847621.78332527</v>
+      </c>
+      <c r="L12" t="n">
+        <v>7432002.297993227</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1250081.372845175</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6181920.925148051</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1664091.949215</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2747016.892772637</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4411108.841987637</v>
+      </c>
+      <c r="U12" t="n">
+        <v>21025725.23887022</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>6181920.925148051</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1770812.083160414</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.401443751807876</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.4631934880846841</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.3219732365906959</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2863425.516383023</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>570154.0978090712</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-23079562.48739772</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-22603542.06528645</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2037</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="K13" t="n">
+        <v>9024574.218991775</v>
+      </c>
+      <c r="L13" t="n">
+        <v>7580642.343953092</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1281333.407166305</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6299308.936786787</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1471800.766720915</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2939308.075266722</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4411108.841987637</v>
+      </c>
+      <c r="U13" t="n">
+        <v>18086417.1636035</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>6299308.936786787</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1888200.09479915</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.4280556573046</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.4288828593376705</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.2874761040988356</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2701665.628660458</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>542812.4070119116</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-16780253.55061093</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-20715341.9704873</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2038</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9205065.70337161</v>
+      </c>
+      <c r="L14" t="n">
+        <v>7732255.190832154</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1313366.742345462</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6418888.448486691</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1266049.201452245</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3145059.640535392</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4411108.841987637</v>
+      </c>
+      <c r="U14" t="n">
+        <v>14941357.5230681</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>6418888.448486691</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2007779.606499054</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.455164376672772</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.3971137586459912</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.2566750929453889</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2549028.918107885</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>515347.0171120011</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-10361365.10212424</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-18707562.36398825</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2039</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>12</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="I15" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="K15" t="n">
+        <v>9389167.017439043</v>
+      </c>
+      <c r="L15" t="n">
+        <v>7886900.294648797</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1346200.910904099</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6540699.383744699</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1045895.026614767</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3365213.815372869</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4411108.841987637</v>
+      </c>
+      <c r="U15" t="n">
+        <v>11576143.70769523</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>6540699.383744699</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2129590.541757062</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.482778960583859</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.367697924672214</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.2291741901298115</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2405001.589307755</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>488047.1877152812</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-3820665.718379539</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-16577971.82223118</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>13</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="I16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="K16" t="n">
+        <v>9576950.357787823</v>
+      </c>
+      <c r="L16" t="n">
+        <v>8044638.300541773</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1379855.933676701</v>
+      </c>
+      <c r="N16" t="n">
+        <v>6664782.366865071</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>810330.0595386665</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3600778.78244897</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4411108.841987637</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7975364.925246265</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>6664782.366865071</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2253673.524877435</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.510908618582609</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.3404610413631611</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.2046198126159031</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2269098.745081716</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>461146.2543578426</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2844116.648485532</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-14324298.29735375</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2041</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9768489.364943581</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8205531.066552608</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1414352.332018618</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6791178.73453399</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>558275.5447672385</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3852833.297220398</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4411108.841987637</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4122531.628025867</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>6791178.73453399</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2380069.892546353</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.53956272171101</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.3152417049658899</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.1826962612641992</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2140862.76300259</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>434829.870915703</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>9635295.383019522</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-11944228.4048074</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2042</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>52.44</v>
+      </c>
+      <c r="K18" t="n">
+        <v>9963859.152242452</v>
+      </c>
+      <c r="L18" t="n">
+        <v>8369641.68788366</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1449711.140319084</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6919930.547564576</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>288577.2139618107</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4122531.628025826</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4411108.841987637</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4.051253199577332e-08</v>
+      </c>
+      <c r="V18" t="n">
+        <v>82850197.0830677</v>
+      </c>
+      <c r="W18" t="n">
+        <v>89770127.63063228</v>
+      </c>
+      <c r="X18" t="n">
+        <v>85359018.7886446</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.568750805170899</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.2918904675610092</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.163121661843035</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>26203044.52711672</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>13923904.99809455</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>99405423.0136518</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>73414790.38383719</v>
       </c>
     </row>
   </sheetData>
@@ -7888,7 +12046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE7"/>
+  <dimension ref="A1:AE18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8224,16 +12382,16 @@
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9174311926605504</v>
+        <v>0.9259259259259258</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8849557522123894</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="AB3" t="n">
-        <v>-22069724.7706422</v>
+        <v>-22274074.07407407</v>
       </c>
       <c r="AC3" t="n">
-        <v>-8515398.230088497</v>
+        <v>-8591428.571428571</v>
       </c>
       <c r="AD3" t="n">
         <v>-60140000</v>
@@ -8323,16 +12481,16 @@
         <v>0.5438723944666876</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.84167999326656</v>
+        <v>0.8573388203017832</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7831466833737961</v>
+        <v>0.7971938775510203</v>
       </c>
       <c r="AB4" t="n">
-        <v>1678588.67098729</v>
+        <v>1709817.558299039</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1309874.652225952</v>
+        <v>-1333369.693421012</v>
       </c>
       <c r="AD4" t="n">
         <v>-58145668.8</v>
@@ -8422,16 +12580,16 @@
         <v>1.243909403173084</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7721834800610642</v>
+        <v>0.7938322410201696</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.6930501622776957</v>
+        <v>0.7117802478134109</v>
       </c>
       <c r="AB5" t="n">
-        <v>3522163.602513921</v>
+        <v>3620910.182644922</v>
       </c>
       <c r="AC5" t="n">
-        <v>619859.8129822735</v>
+        <v>636611.8865683388</v>
       </c>
       <c r="AD5" t="n">
         <v>-53584364.792</v>
@@ -8521,16 +12679,16 @@
         <v>1.82081593830371</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7084252110651963</v>
+        <v>0.7350298527964533</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6133187276793768</v>
+        <v>0.6355180784048311</v>
       </c>
       <c r="AB6" t="n">
-        <v>4729991.08672151</v>
+        <v>4907624.118816811</v>
       </c>
       <c r="AC6" t="n">
-        <v>1846002.456950337</v>
+        <v>1912819.356765132</v>
       </c>
       <c r="AD6" t="n">
         <v>-46907596.35851999</v>
@@ -8608,34 +12766,1123 @@
         <v>29218594.78138983</v>
       </c>
       <c r="V7" t="n">
-        <v>116978453.6600438</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>124724589.4913304</v>
+        <v>7746135.831286602</v>
       </c>
       <c r="X7" t="n">
-        <v>91839084.56651329</v>
+        <v>4079225.687859285</v>
       </c>
       <c r="Y7" t="n">
         <v>2.112442227462545</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6499313862983452</v>
+        <v>0.6805831970337529</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5427599359994485</v>
+        <v>0.5674268557185992</v>
       </c>
       <c r="AB7" t="n">
-        <v>81062425.3535924</v>
+        <v>5271889.888714743</v>
       </c>
       <c r="AC7" t="n">
-        <v>49846575.66156869</v>
+        <v>2314662.205828534</v>
       </c>
       <c r="AD7" t="n">
-        <v>77816993.13281041</v>
+        <v>-39161460.52723339</v>
       </c>
       <c r="AE7" t="n">
-        <v>70014757.77771133</v>
+        <v>-17745101.10094267</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2032</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9595371.422822399</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8923695.423224831</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1027649.801171875</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7896045.622052956</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1694678.49732061</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1972231.646106707</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3666910.143427317</v>
+      </c>
+      <c r="U8" t="n">
+        <v>27246363.13528312</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7896045.622052956</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4229135.478625639</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.15332400119105</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.6301696268831045</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.5066311211773206</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4975848.123501083</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2142611.649146892</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-31265414.90518044</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-13515965.62231703</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2033</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9787278.851278849</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9102169.33168933</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1053341.046201171</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8048828.285488158</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1580289.061846421</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2086621.081580896</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3666910.143427317</v>
+      </c>
+      <c r="U9" t="n">
+        <v>25159742.05370222</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8048828.285488158</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4381918.142060841</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.194989233623607</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.5834903952621338</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.4523492153368934</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>4696413.997696528</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1982157.233231719</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-23216586.61969228</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-9134047.480256185</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2034</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I10" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9983024.428304426</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9284212.718323117</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1079674.572356201</v>
+      </c>
+      <c r="N10" t="n">
+        <v>8204538.145966916</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1459265.039114729</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2207645.104312588</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3666910.143427317</v>
+      </c>
+      <c r="U10" t="n">
+        <v>22952096.94938963</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>8204538.145966916</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4537628.002539599</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.237452739515034</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.5402688845019757</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.403883227979369</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4432656.671975454</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1832671.84503527</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-15012048.47372536</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-4596419.477716586</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2035</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I11" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10182684.91687051</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9469896.972689578</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1106666.436665106</v>
+      </c>
+      <c r="N11" t="n">
+        <v>8363230.536024473</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1331221.623064599</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2335688.520362718</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3666910.143427317</v>
+      </c>
+      <c r="U11" t="n">
+        <v>20616408.42902691</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>8363230.536024473</v>
+      </c>
+      <c r="X11" t="n">
+        <v>4696320.392597156</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.280729608554763</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.5002489671314589</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.3606100249815795</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4183697.43752852</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1693540.214095961</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-6648817.937700887</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>99900.91488057002</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2036</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10386338.61520793</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9659294.912143372</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1134333.097581733</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8524961.814561639</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1195751.688883561</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2471158.454543756</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3666910.143427317</v>
+      </c>
+      <c r="U12" t="n">
+        <v>18145249.97448315</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>8524961.814561639</v>
+      </c>
+      <c r="X12" t="n">
+        <v>4858051.671134322</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.324835210331522</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.4631934880846841</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.3219732365906959</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3948706.798675544</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1564162.620079957</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1876143.876860752</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>4957952.586014892</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2037</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="K13" t="n">
+        <v>10594065.38751208</v>
+      </c>
+      <c r="L13" t="n">
+        <v>9852480.810386239</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1162691.425021276</v>
+      </c>
+      <c r="N13" t="n">
+        <v>8689789.385364963</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1052424.498520023</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2614485.644907294</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3666910.143427317</v>
+      </c>
+      <c r="U13" t="n">
+        <v>15530764.32957586</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>8689789.385364963</v>
+      </c>
+      <c r="X13" t="n">
+        <v>5022879.241937646</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.369785199383958</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.4288828593376705</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.2874761040988356</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3726901.718637464</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1443957.755831147</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>10565933.26222571</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>9980831.827952538</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2038</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="K14" t="n">
+        <v>10805946.69526233</v>
+      </c>
+      <c r="L14" t="n">
+        <v>10049530.42659396</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1191758.710646808</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8857771.715947155</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>900784.3311153998</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2766125.812311917</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3666910.143427317</v>
+      </c>
+      <c r="U14" t="n">
+        <v>12764638.51726394</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>8857771.715947155</v>
+      </c>
+      <c r="X14" t="n">
+        <v>5190861.572519838</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.415595520338587</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.3971137586459912</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.2566750929453889</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3517543.019347926</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1332364.876593177</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>19423704.97817287</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>15171693.40047238</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2039</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>12</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I15" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="K15" t="n">
+        <v>11022065.62916757</v>
+      </c>
+      <c r="L15" t="n">
+        <v>10250521.03512584</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1221552.678412978</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9028968.356712865</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>740349.0340013086</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2926561.109426009</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3666910.143427317</v>
+      </c>
+      <c r="U15" t="n">
+        <v>9838077.407837935</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>9028968.356712865</v>
+      </c>
+      <c r="X15" t="n">
+        <v>5362058.213285548</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.462282413136484</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.367697924672214</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.2291741901298115</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3319932.926694411</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1228845.348458619</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>28452673.33488573</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>20533751.61375792</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>13</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="K16" t="n">
+        <v>11242506.94175092</v>
+      </c>
+      <c r="L16" t="n">
+        <v>10455531.45582836</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1252091.495373303</v>
+      </c>
+      <c r="N16" t="n">
+        <v>9203439.960455056</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>570608.4896546002</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3096301.653772717</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3666910.143427317</v>
+      </c>
+      <c r="U16" t="n">
+        <v>6741775.754065217</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>9203439.960455056</v>
+      </c>
+      <c r="X16" t="n">
+        <v>5536529.817027739</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.509862418350116</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.3404610413631611</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.2046198126159031</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3133412.753059859</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1132883.693702576</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>37656113.29534079</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>26070281.43078566</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2041</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="K17" t="n">
+        <v>11467357.08058594</v>
+      </c>
+      <c r="L17" t="n">
+        <v>10664642.08494493</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1283393.782757635</v>
+      </c>
+      <c r="N17" t="n">
+        <v>9381248.302187294</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>391022.9937357826</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3275887.149691534</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3666910.143427317</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3465888.604373683</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>9381248.302187294</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5714338.158759977</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.558352382591794</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.3152417049658899</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.1826962612641992</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2957360.709489883</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1043988.217204796</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>47037361.59752809</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>31784619.58954564</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Build-to-exit</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2042</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="K18" t="n">
+        <v>11696704.22219766</v>
+      </c>
+      <c r="L18" t="n">
+        <v>10877934.92664383</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1315478.627326576</v>
+      </c>
+      <c r="N18" t="n">
+        <v>9562456.29931725</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>201021.5390536736</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3465888.604373643</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3666910.143427317</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4.004687070846558e-08</v>
+      </c>
+      <c r="V18" t="n">
+        <v>135737782.9664733</v>
+      </c>
+      <c r="W18" t="n">
+        <v>145300239.2657905</v>
+      </c>
+      <c r="X18" t="n">
+        <v>141633329.1223632</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.607769464015171</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.2918904675610092</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.163121661843035</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>42411754.77601809</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>23103464.0188014</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>192337600.8633186</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>173417948.7119088</v>
       </c>
     </row>
   </sheetData>
@@ -8706,28 +13953,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28408.42275715671</v>
+        <v>9557592.320047902</v>
       </c>
       <c r="C2" t="n">
-        <v>11476496.42104789</v>
+        <v>21665947.57370891</v>
       </c>
       <c r="D2" t="n">
-        <v>21778364.66325273</v>
+        <v>32471435.50269955</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1173701195573514</v>
+        <v>0.1068941091486869</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1371151056262404</v>
+        <v>0.1217619256822144</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1541587126212635</v>
+        <v>0.1345556920802673</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.835</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -8737,28 +13984,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6795656.391481164</v>
+        <v>13160284.45303204</v>
       </c>
       <c r="C3" t="n">
-        <v>12668335.42471619</v>
+        <v>19442470.28487743</v>
       </c>
       <c r="D3" t="n">
-        <v>17910236.89631648</v>
+        <v>25063635.61342104</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1379939716882215</v>
+        <v>0.124731095694059</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1565107770016579</v>
+        <v>0.1391959897179562</v>
       </c>
       <c r="G3" t="n">
-        <v>0.172902857986614</v>
+        <v>0.1518500866784265</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.318</v>
+        <v>0.863</v>
       </c>
     </row>
     <row r="4">
@@ -8768,28 +14015,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1683986.958542801</v>
+        <v>7247042.818909189</v>
       </c>
       <c r="C4" t="n">
-        <v>5852719.178494819</v>
+        <v>14934295.52962073</v>
       </c>
       <c r="D4" t="n">
-        <v>12471460.63315304</v>
+        <v>21570613.04913255</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1155623141175506</v>
+        <v>0.1098644740726058</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1726802442380224</v>
+        <v>0.1276089390706521</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2187850308068252</v>
+        <v>0.1424711477408998</v>
       </c>
       <c r="H4" t="n">
-        <v>0.155</v>
+        <v>0.005</v>
       </c>
       <c r="I4" t="n">
-        <v>0.298</v>
+        <v>0.9785</v>
       </c>
     </row>
   </sheetData>
@@ -8865,13 +14112,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C2" t="n">
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -8899,16 +14146,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
         <v>3</v>
       </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -9227,7 +14474,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-15466561.34730775</v>
+        <v>-16673734.128169</v>
       </c>
     </row>
     <row r="3">
@@ -9237,27 +14484,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-11506972.47706423</v>
+        <v>-11547407.40740742</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>exit_yield_+100bps</t>
+          <t>occupancy_-5pts</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-9695734.837643251</v>
+        <v>-9302305.257937014</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>occupancy_-5pts</t>
+          <t>exit_yield_+100bps</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-8654757.457368694</v>
+        <v>-7551634.33878085</v>
       </c>
     </row>
     <row r="6">
@@ -9273,21 +14520,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>capex_-5pct</t>
+          <t>exit_yield_-50bps</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5753486.238532096</v>
+        <v>4682013.290044121</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>exit_yield_-50bps</t>
+          <t>capex_-5pct</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6011355.599338815</v>
+        <v>5773703.703703709</v>
       </c>
     </row>
     <row r="9">
@@ -9297,7 +14544,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15466561.34730778</v>
+        <v>16673734.12816901</v>
       </c>
     </row>
   </sheetData>
@@ -9333,7 +14580,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-8110325.857533682</v>
+        <v>-8905480.462695546</v>
       </c>
     </row>
     <row r="3">
@@ -9343,7 +14590,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-5511743.119266056</v>
+        <v>-5531111.111111116</v>
       </c>
     </row>
     <row r="4">
@@ -9353,7 +14600,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-4738501.785620958</v>
+        <v>-5169840.521450453</v>
       </c>
     </row>
     <row r="5">
@@ -9363,7 +14610,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-4609888.263863496</v>
+        <v>-3590752.117569633</v>
       </c>
     </row>
     <row r="6">
@@ -9379,21 +14626,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>capex_-5pct</t>
+          <t>exit_yield_-50bps</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2755871.559633024</v>
+        <v>2180099.499952994</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>exit_yield_-50bps</t>
+          <t>capex_-5pct</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2798860.731631406</v>
+        <v>2765555.555555552</v>
       </c>
     </row>
     <row r="9">
@@ -9403,7 +14650,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8110325.857533667</v>
+        <v>8905480.462695554</v>
       </c>
     </row>
   </sheetData>
@@ -9439,37 +14686,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-8743893.072151385</v>
+        <v>-9628248.472782228</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>exit_yield_+100bps</t>
+          <t>capex_+10pct</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-7549277.657616295</v>
+        <v>-6016296.29629628</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>capex_+10pct</t>
+          <t>occupancy_-5pts</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-5995229.357798159</v>
+        <v>-5736619.013863433</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>occupancy_-5pts</t>
+          <t>exit_yield_+100bps</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-5236541.852139279</v>
+        <v>-3929613.776254881</v>
       </c>
     </row>
     <row r="6">
@@ -9485,21 +14732,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>capex_-5pct</t>
+          <t>exit_yield_-50bps</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2997614.67889908</v>
+        <v>2401430.641044661</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>exit_yield_-50bps</t>
+          <t>capex_-5pct</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4613447.457432188</v>
+        <v>3008148.148148157</v>
       </c>
     </row>
     <row r="9">
@@ -9509,7 +14756,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8743893.072151378</v>
+        <v>9628248.472782217</v>
       </c>
     </row>
   </sheetData>
@@ -9523,7 +14770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE13"/>
+  <dimension ref="A1:AE18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9859,16 +15106,16 @@
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9174311926605504</v>
+        <v>0.9259259259259258</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8849557522123894</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="AB3" t="n">
-        <v>-43669724.7706422</v>
+        <v>-44074074.07407407</v>
       </c>
       <c r="AC3" t="n">
-        <v>-16849557.5221239</v>
+        <v>-17000000</v>
       </c>
       <c r="AD3" t="n">
         <v>-119000000</v>
@@ -9958,16 +15205,16 @@
         <v>0.507733496709994</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.84167999326656</v>
+        <v>0.8573388203017832</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7831466833737961</v>
+        <v>0.7971938775510203</v>
       </c>
       <c r="AB4" t="n">
-        <v>3100749.095194007</v>
+        <v>3158436.213991769</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2797223.726357908</v>
+        <v>-2847397.143005749</v>
       </c>
       <c r="AD4" t="n">
         <v>-115316000</v>
@@ -10057,16 +15304,16 @@
         <v>1.063420520250953</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7721834800610642</v>
+        <v>0.7938322410201696</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.6930501622776957</v>
+        <v>0.7117802478134109</v>
       </c>
       <c r="AB5" t="n">
-        <v>5958121.401142367</v>
+        <v>6125161.941777167</v>
       </c>
       <c r="AC5" t="n">
-        <v>318917.4444285273</v>
+        <v>327536.3746851002</v>
       </c>
       <c r="AD5" t="n">
         <v>-107600060</v>
@@ -10156,16 +15403,16 @@
         <v>1.362378096405017</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7084252110651963</v>
+        <v>0.7350298527964533</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6133187276793768</v>
+        <v>0.6355180784048311</v>
       </c>
       <c r="AB6" t="n">
-        <v>7002860.35888495</v>
+        <v>7265850.13964391</v>
       </c>
       <c r="AC6" t="n">
-        <v>1612619.736797574</v>
+        <v>1670989.242746647</v>
       </c>
       <c r="AD6" t="n">
         <v>-97714951.09999999</v>
@@ -10255,16 +15502,16 @@
         <v>1.521224035244451</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6499313862983452</v>
+        <v>0.6805831970337529</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5427599359994485</v>
+        <v>0.5674268557185992</v>
       </c>
       <c r="AB7" t="n">
-        <v>7173721.202603641</v>
+        <v>7512045.446064397</v>
       </c>
       <c r="AC7" t="n">
-        <v>2052655.287091539</v>
+        <v>2145942.723800627</v>
       </c>
       <c r="AD7" t="n">
         <v>-86677291.81189999</v>
@@ -10354,16 +15601,16 @@
         <v>1.608537400386251</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5962673268792158</v>
+        <v>0.6301696268831045</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.4803185274331404</v>
+        <v>0.5066311211773206</v>
       </c>
       <c r="AB8" t="n">
-        <v>6959146.530692108</v>
+        <v>7354826.560133562</v>
       </c>
       <c r="AC8" t="n">
-        <v>2120803.441416409</v>
+        <v>2236984.342585201</v>
       </c>
       <c r="AD8" t="n">
         <v>-75006106.39391749</v>
@@ -10453,16 +15700,16 @@
         <v>1.639567181825021</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.5470342448433172</v>
+        <v>0.5834903952621338</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.4250606437461419</v>
+        <v>0.4523492153368934</v>
       </c>
       <c r="AB9" t="n">
-        <v>6507700.187700406</v>
+        <v>6941394.60292174</v>
       </c>
       <c r="AC9" t="n">
-        <v>1972517.530900265</v>
+        <v>2099151.663342155</v>
       </c>
       <c r="AD9" t="n">
         <v>-63109775.86425503</v>
@@ -10552,16 +15799,16 @@
         <v>1.671189034728343</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.501866279672768</v>
+        <v>0.5402688845019757</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.3761598617222495</v>
+        <v>0.403883227979369</v>
       </c>
       <c r="AB10" t="n">
-        <v>6085515.870343396</v>
+        <v>6551177.084527878</v>
       </c>
       <c r="AC10" t="n">
-        <v>1831897.248573927</v>
+        <v>1966909.948055203</v>
       </c>
       <c r="AD10" t="n">
         <v>-50984004.28559599</v>
@@ -10651,16 +15898,16 @@
         <v>1.703414087421401</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.4604277795163009</v>
+        <v>0.5002489671314589</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.3328848333825217</v>
+        <v>0.3606100249815795</v>
       </c>
       <c r="AB11" t="n">
-        <v>5690698.261550519</v>
+        <v>6182871.786294228</v>
       </c>
       <c r="AC11" t="n">
-        <v>1698982.383992249</v>
+        <v>1840486.614272036</v>
       </c>
       <c r="AD11" t="n">
         <v>-38624414.97600038</v>
@@ -10750,16 +15997,16 @@
         <v>1.736253672968284</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.4224108068956888</v>
+        <v>0.4631934880846841</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.2945883481261255</v>
+        <v>0.3219732365906959</v>
       </c>
       <c r="AB12" t="n">
-        <v>5321474.722216284</v>
+        <v>5835249.473024297</v>
       </c>
       <c r="AC12" t="n">
-        <v>1573717.756291476</v>
+        <v>1720010.321849109</v>
       </c>
       <c r="AD12" t="n">
         <v>-26026549.02336536</v>
@@ -10837,34 +16084,529 @@
         <v>30730976.97405268</v>
       </c>
       <c r="V13" t="n">
-        <v>193898259.0026802</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>206738944.2526366</v>
+        <v>12840685.2499564</v>
       </c>
       <c r="X13" t="n">
-        <v>168752192.3023975</v>
+        <v>5584910.273769984</v>
       </c>
       <c r="Y13" t="n">
         <v>1.769719332821065</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.3875328503630173</v>
+        <v>0.4288828593376705</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.2606976532089606</v>
+        <v>0.2874761040988356</v>
       </c>
       <c r="AB13" t="n">
-        <v>80118132.34726521</v>
+        <v>5507149.805856349</v>
       </c>
       <c r="AC13" t="n">
-        <v>43993300.50710227</v>
+        <v>1605528.247244956</v>
       </c>
       <c r="AD13" t="n">
-        <v>180712395.2292713</v>
+        <v>-13185863.77340896</v>
       </c>
       <c r="AE13" t="n">
-        <v>148823668.4933545</v>
+        <v>-14343613.53527308</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Turnkey</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2038</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>90</v>
+      </c>
+      <c r="K14" t="n">
+        <v>15798167.68313205</v>
+      </c>
+      <c r="L14" t="n">
+        <v>15008259.29897545</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1920126.816294535</v>
+      </c>
+      <c r="N14" t="n">
+        <v>13088132.48268092</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1782396.664495055</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5473378.311691356</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7255774.976186411</v>
+      </c>
+      <c r="U14" t="n">
+        <v>25257598.66236132</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13088132.48268092</v>
+      </c>
+      <c r="X14" t="n">
+        <v>5832357.506494505</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.803822820530737</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.3971137586459912</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.2566750929453889</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>5197477.483854107</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1497020.905070214</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-97731.29072804376</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-8511256.028778579</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Turnkey</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2039</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>12</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I15" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>90</v>
+      </c>
+      <c r="K15" t="n">
+        <v>16114131.0367947</v>
+      </c>
+      <c r="L15" t="n">
+        <v>15308424.48495496</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1968129.986701898</v>
+      </c>
+      <c r="N15" t="n">
+        <v>13340294.49825306</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1464940.722416957</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5790834.253769455</v>
+      </c>
+      <c r="T15" t="n">
+        <v>7255774.976186411</v>
+      </c>
+      <c r="U15" t="n">
+        <v>19466764.40859187</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>13340294.49825306</v>
+      </c>
+      <c r="X15" t="n">
+        <v>6084519.522066651</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.838576105520934</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.367697924672214</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.2291741901298115</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>4905198.601523805</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1394414.833798653</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>13242563.20752502</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-2426736.506711928</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Turnkey</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>13</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>90</v>
+      </c>
+      <c r="K16" t="n">
+        <v>16436413.65753059</v>
+      </c>
+      <c r="L16" t="n">
+        <v>15614592.97465406</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2017333.236369446</v>
+      </c>
+      <c r="N16" t="n">
+        <v>13597259.73828461</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1129072.335698328</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6126702.640488083</v>
+      </c>
+      <c r="T16" t="n">
+        <v>7255774.976186411</v>
+      </c>
+      <c r="U16" t="n">
+        <v>13340061.76810378</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>13597259.73828461</v>
+      </c>
+      <c r="X16" t="n">
+        <v>6341484.762098201</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.873991376925424</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.3404610413631611</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.2046198126159031</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>4629337.210181762</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1297593.423727139</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>26839822.94580963</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>3914748.255386272</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Turnkey</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2041</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>90</v>
+      </c>
+      <c r="K17" t="n">
+        <v>16765141.9306812</v>
+      </c>
+      <c r="L17" t="n">
+        <v>15926884.83414714</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2067766.567278681</v>
+      </c>
+      <c r="N17" t="n">
+        <v>13859118.26686846</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>773723.5825500194</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6482051.393636392</v>
+      </c>
+      <c r="T17" t="n">
+        <v>7255774.976186411</v>
+      </c>
+      <c r="U17" t="n">
+        <v>6858010.37446739</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>13859118.26686846</v>
+      </c>
+      <c r="X17" t="n">
+        <v>6603343.290682049</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.910081047490357</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.3152417049658899</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.1826962612641992</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>4368972.071771523</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1206406.131051644</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>40698941.21267809</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>10518091.54606832</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Turnkey</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2042</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>90</v>
+      </c>
+      <c r="K18" t="n">
+        <v>17100444.76929482</v>
+      </c>
+      <c r="L18" t="n">
+        <v>16245422.53083008</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2119460.731460649</v>
+      </c>
+      <c r="N18" t="n">
+        <v>14125961.79936943</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>397764.6017191086</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6858010.374467303</v>
+      </c>
+      <c r="T18" t="n">
+        <v>7255774.976186411</v>
+      </c>
+      <c r="U18" t="n">
+        <v>8.66129994392395e-08</v>
+      </c>
+      <c r="V18" t="n">
+        <v>200503862.3377415</v>
+      </c>
+      <c r="W18" t="n">
+        <v>214629824.1371109</v>
+      </c>
+      <c r="X18" t="n">
+        <v>207374049.1609244</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.946857757542248</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.2918904675610092</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.163121661843035</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>62648399.71991847</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>33827199.52224922</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>255328765.349789</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>217892140.7069927</v>
       </c>
     </row>
   </sheetData>
@@ -10878,7 +16620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE13"/>
+  <dimension ref="A1:AE18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11214,16 +16956,16 @@
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0.9174311926605504</v>
+        <v>0.9259259259259258</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8849557522123894</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="AB3" t="n">
-        <v>-47163302.75229358</v>
+        <v>-47600000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-18197522.12389381</v>
+        <v>-18360000</v>
       </c>
       <c r="AD3" t="n">
         <v>-128520000</v>
@@ -11313,16 +17055,16 @@
         <v>0.2948794692125012</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.84167999326656</v>
+        <v>0.8573388203017832</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.7831466833737961</v>
+        <v>0.7971938775510203</v>
       </c>
       <c r="AB4" t="n">
-        <v>2048554.835451561</v>
+        <v>2086666.666666667</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4557876.217301143</v>
+        <v>-4639630.215140169</v>
       </c>
       <c r="AD4" t="n">
         <v>-126086112</v>
@@ -11412,16 +17154,16 @@
         <v>0.741832268950561</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7721834800610642</v>
+        <v>0.7938322410201696</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.6930501622776957</v>
+        <v>0.7117802478134109</v>
       </c>
       <c r="AB5" t="n">
-        <v>4728052.391104754</v>
+        <v>4860606.995884772</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1476803.390589786</v>
+        <v>-1516714.865012178</v>
       </c>
       <c r="AD5" t="n">
         <v>-119963147.04</v>
@@ -11511,16 +17253,16 @@
         <v>0.9811016704963158</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7084252110651963</v>
+        <v>0.7350298527964533</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6133187276793768</v>
+        <v>0.6355180784048311</v>
       </c>
       <c r="AB6" t="n">
-        <v>5736725.5947745</v>
+        <v>5952166.16178936</v>
       </c>
       <c r="AC6" t="n">
-        <v>-95667.78003345248</v>
+        <v>-99130.51891006227</v>
       </c>
       <c r="AD6" t="n">
         <v>-111865290.6888</v>
@@ -11610,16 +17352,16 @@
         <v>1.107001459255774</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6499313862983452</v>
+        <v>0.6805831970337529</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5427599359994485</v>
+        <v>0.5674268557185992</v>
       </c>
       <c r="AB7" t="n">
-        <v>5938431.578695811</v>
+        <v>6218497.574357384</v>
       </c>
       <c r="AC7" t="n">
-        <v>479350.888197717</v>
+        <v>501136.0441980462</v>
       </c>
       <c r="AD7" t="n">
         <v>-102728277.607284</v>
@@ -11709,16 +17451,16 @@
         <v>1.174993944187025</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5962673268792158</v>
+        <v>0.6301696268831045</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.4803185274331404</v>
+        <v>0.5066311211773206</v>
       </c>
       <c r="AB8" t="n">
-        <v>5782727.053857208</v>
+        <v>6111518.752786208</v>
       </c>
       <c r="AC8" t="n">
-        <v>693758.6518541238</v>
+        <v>731763.8265874443</v>
       </c>
       <c r="AD8" t="n">
         <v>-93030065.42429683</v>
@@ -11808,16 +17550,16 @@
         <v>1.197410583722732</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.5470342448433172</v>
+        <v>0.5834903952621338</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.4250606437461419</v>
+        <v>0.4523492153368934</v>
       </c>
       <c r="AB9" t="n">
-        <v>5406468.291453985</v>
+        <v>5766773.013006221</v>
       </c>
       <c r="AC9" t="n">
-        <v>692591.8577944626</v>
+        <v>737055.7308268558</v>
       </c>
       <c r="AD9" t="n">
         <v>-83146829.88206397</v>
@@ -11907,16 +17649,16 @@
         <v>1.220248475065451</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.501866279672768</v>
+        <v>0.5402688845019757</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.3761598617222495</v>
+        <v>0.403883227979369</v>
       </c>
       <c r="AB10" t="n">
-        <v>5054664.599156463</v>
+        <v>5441445.490815808</v>
       </c>
       <c r="AC10" t="n">
-        <v>683819.3968983799</v>
+        <v>734217.5853365033</v>
       </c>
       <c r="AD10" t="n">
         <v>-73075094.03551087</v>
@@ -12006,16 +17748,16 @@
         <v>1.243515366226731</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.4604277795163009</v>
+        <v>0.5002489671314589</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.3328848333825217</v>
+        <v>0.3606100249815795</v>
       </c>
       <c r="AB11" t="n">
-        <v>4725728.075106954</v>
+        <v>5134443.866527596</v>
       </c>
       <c r="AC11" t="n">
-        <v>669077.511705278</v>
+        <v>724803.3974963356</v>
       </c>
       <c r="AD11" t="n">
         <v>-62811316.98871423</v>
@@ -12105,16 +17847,16 @@
         <v>1.267219143252736</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.4224108068956888</v>
+        <v>0.4631934880846841</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.2945883481261255</v>
+        <v>0.3219732365906959</v>
       </c>
       <c r="AB12" t="n">
-        <v>4418173.829979862</v>
+        <v>4844737.193899968</v>
       </c>
       <c r="AC12" t="n">
-        <v>649739.3740963772</v>
+        <v>710139.0484346546</v>
       </c>
       <c r="AD12" t="n">
         <v>-52351892.75558636</v>
@@ -12192,34 +17934,529 @@
         <v>34207940.74512401</v>
       </c>
       <c r="V13" t="n">
-        <v>144824036.4980057</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>155482780.1523263</v>
+        <v>10658743.65432059</v>
       </c>
       <c r="X13" t="n">
-        <v>113020999.2653304</v>
+        <v>2404903.512448762</v>
       </c>
       <c r="Y13" t="n">
         <v>1.291367832561799</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.3875328503630173</v>
+        <v>0.4288828593376705</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.2606976532089606</v>
+        <v>0.2874761040988356</v>
       </c>
       <c r="AB13" t="n">
-        <v>60254684.97479737</v>
+        <v>4571352.455412266</v>
       </c>
       <c r="AC13" t="n">
-        <v>29464309.2718033</v>
+        <v>691352.2924923756</v>
       </c>
       <c r="AD13" t="n">
-        <v>103130887.3967399</v>
+        <v>-41693149.10126577</v>
       </c>
       <c r="AE13" t="n">
-        <v>63496545.23289759</v>
+        <v>-47119550.51998405</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Turnkey</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2038</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="K14" t="n">
+        <v>14534314.26848149</v>
+      </c>
+      <c r="L14" t="n">
+        <v>12935539.69894852</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2073736.961598098</v>
+      </c>
+      <c r="N14" t="n">
+        <v>10861802.73735043</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2257724.089178185</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5996116.052693644</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8253840.141871829</v>
+      </c>
+      <c r="U14" t="n">
+        <v>28211824.69243037</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>10861802.73735043</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2607962.595478598</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.315969603318142</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.3971137586459912</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.2566750929453889</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>4313371.310700544</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>669399.0415925668</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-30831346.36391535</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-44511587.92450546</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Turnkey</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2039</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>12</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="I15" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="K15" t="n">
+        <v>14825000.55385112</v>
+      </c>
+      <c r="L15" t="n">
+        <v>13194250.4929275</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2125580.38563805</v>
+      </c>
+      <c r="N15" t="n">
+        <v>11068670.10728944</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1861980.429700404</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6391859.712171424</v>
+      </c>
+      <c r="T15" t="n">
+        <v>8253840.141871829</v>
+      </c>
+      <c r="U15" t="n">
+        <v>21819964.98025895</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>11068670.10728944</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2814829.965417616</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.34103276984224</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.367697924672214</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.2291741901298115</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>4069927.027331701</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>645086.3776777075</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-19762676.2566259</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-41696757.95908784</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Turnkey</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>13</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="I16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>15121500.56492814</v>
+      </c>
+      <c r="L16" t="n">
+        <v>13458135.50278605</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2178719.895279001</v>
+      </c>
+      <c r="N16" t="n">
+        <v>11279415.60750704</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1440117.68869709</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6813722.453174738</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8253840.141871829</v>
+      </c>
+      <c r="U16" t="n">
+        <v>15006242.52708421</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>11279415.60750704</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3025575.465635216</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.366565794058263</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.3404610413631611</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.2046198126159031</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3840201.583699741</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>619092.6848335516</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-8483260.649118857</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-38671182.49345262</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Turnkey</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2041</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="I17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>15423930.57622671</v>
+      </c>
+      <c r="L17" t="n">
+        <v>13727298.21284177</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2233187.892660976</v>
+      </c>
+      <c r="N17" t="n">
+        <v>11494110.32018079</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>990412.0067875577</v>
+      </c>
+      <c r="S17" t="n">
+        <v>7263428.13508427</v>
+      </c>
+      <c r="T17" t="n">
+        <v>8253840.141871829</v>
+      </c>
+      <c r="U17" t="n">
+        <v>7742814.391999937</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>11494110.32018079</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3240270.178308964</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.392577287979087</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.3152417049658899</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.1826962612641992</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3623422.934399824</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>591985.2470629277</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3010849.671061935</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-35430912.31514366</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Turnkey</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Operate</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2042</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.8899999999999999</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>15732409.18775124</v>
+      </c>
+      <c r="L18" t="n">
+        <v>14001844.1770986</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2289017.5899775</v>
+      </c>
+      <c r="N18" t="n">
+        <v>11712826.5871211</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>511025.7498719958</v>
+      </c>
+      <c r="S18" t="n">
+        <v>7742814.391999832</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8253840.141871829</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.043081283569336e-07</v>
+      </c>
+      <c r="V18" t="n">
+        <v>149593329.9874509</v>
+      </c>
+      <c r="W18" t="n">
+        <v>161306156.574572</v>
+      </c>
+      <c r="X18" t="n">
+        <v>153052316.4327</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.419076016229318</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.2918904675610092</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.163121661843035</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>47083729.46302117</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>24966148.20542808</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>164317006.2456339</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>117621404.1175564</v>
       </c>
     </row>
   </sheetData>
